--- a/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
+++ b/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:12:45+00:00</t>
+    <t>2025-04-24T12:14:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
+++ b/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:14:49+00:00</t>
+    <t>2025-04-24T12:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
+++ b/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:53:37+00:00</t>
+    <t>2025-04-25T09:56:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
+++ b/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/type-venue-encounter-vs</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/type-venue-encounter-vs</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T09:56:34+00:00</t>
+    <t>2025-04-25T14:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
+++ b/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T14:29:23+00:00</t>
+    <t>2025-04-25T16:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
+++ b/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/type-venue-encounter-vs</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/type-venue-encounter-vs</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T16:50:14+00:00</t>
+    <t>2025-04-28T06:55:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
+++ b/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
   <si>
     <t>Property</t>
   </si>
@@ -54,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T06:55:35+00:00</t>
+    <t>2025-04-28T10:41:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -316,74 +319,76 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -405,7 +410,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -413,51 +418,51 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
+++ b/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T16:12:30+00:00</t>
+    <t>2025-05-26T06:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
+++ b/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T06:59:47+00:00</t>
+    <t>2025-06-02T15:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
+++ b/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T15:02:23+00:00</t>
+    <t>2025-10-22T09:09:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,16 +111,16 @@
     <t>Teleconsultation</t>
   </si>
   <si>
-    <t>SS</t>
-  </si>
-  <si>
-    <t>Outpatient</t>
-  </si>
-  <si>
-    <t>NONAC</t>
-  </si>
-  <si>
-    <t>Inpatient</t>
+    <t>AMB</t>
+  </si>
+  <si>
+    <t>Consultation externe</t>
+  </si>
+  <si>
+    <t>IMP</t>
+  </si>
+  <si>
+    <t>Hospitalisation</t>
   </si>
   <si>
     <t/>

--- a/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
+++ b/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-22T09:09:51+00:00</t>
+    <t>2025-10-28T10:00:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
+++ b/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T10:00:18+00:00</t>
+    <t>2025-11-19T09:47:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
+++ b/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T09:47:12+00:00</t>
+    <t>2026-01-14T12:51:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
+++ b/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T12:51:21+00:00</t>
+    <t>2026-02-24T09:27:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
+++ b/nmoreau/ig/ValueSet-type-venue-encounter-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T09:27:09+00:00</t>
+    <t>2026-04-10T11:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
